--- a/results_compare/data/2018_eia_monthly_data_hawaii_residential.xlsx
+++ b/results_compare/data/2018_eia_monthly_data_hawaii_residential.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lliu2/Documents/GitHub/resstock4/results_compare/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F151401-D8FD-A14A-936C-598295BCF670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041AD9D7-4B90-E841-92C8-35F64F2A3762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35380" yWindow="4080" windowWidth="29520" windowHeight="20680" activeTab="3" xr2:uid="{DD0B7EDA-CF3D-F54D-9EA5-4986560C9F35}"/>
+    <workbookView xWindow="-39940" yWindow="2540" windowWidth="29520" windowHeight="24420" activeTab="2" xr2:uid="{DD0B7EDA-CF3D-F54D-9EA5-4986560C9F35}"/>
   </bookViews>
   <sheets>
     <sheet name="retail_sales" sheetId="1" r:id="rId1"/>
     <sheet name="net_metering" sheetId="3" r:id="rId2"/>
-    <sheet name="small_scale_solar" sheetId="2" r:id="rId3"/>
-    <sheet name="natural_gas_kbtu" sheetId="4" r:id="rId4"/>
+    <sheet name="non_net_metering" sheetId="5" r:id="rId3"/>
+    <sheet name="small_scale_solar" sheetId="2" r:id="rId4"/>
+    <sheet name="natural_gas_kbtu" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">retail_sales!$A$1:$I$61</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="45">
   <si>
     <t>Year</t>
   </si>
@@ -175,13 +176,17 @@
   <si>
     <t>Customers</t>
   </si>
+  <si>
+    <t>.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -264,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -309,6 +314,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4503,6 +4514,1290 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791B1EF4-54C6-604F-9E89-51B670D024E2}">
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="42" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.879</v>
+      </c>
+      <c r="H2" s="17">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H3" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="16">
+        <v>2.7309999999999999</v>
+      </c>
+      <c r="H4" s="17">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="16">
+        <v>6.2E-2</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="H6" s="17">
+        <v>0.64700000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="16">
+        <v>2.9239999999999999</v>
+      </c>
+      <c r="H8" s="17">
+        <v>0.97199999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="16">
+        <v>6.2E-2</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="H10" s="17">
+        <v>0.69699999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B11" s="4">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="16">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1.032</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="16">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B14" s="4">
+        <v>4</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B15" s="4">
+        <v>4</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="4">
+        <v>4</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="16">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1.0680000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B17" s="4">
+        <v>4</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="16">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="16">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0.95499999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B20" s="4">
+        <v>5</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="16">
+        <v>3.1259999999999999</v>
+      </c>
+      <c r="H20" s="17">
+        <v>1.163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B21" s="4">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="16">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B22" s="4">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="16">
+        <v>1.484</v>
+      </c>
+      <c r="H22" s="17">
+        <v>1.2549999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B23" s="4">
+        <v>6</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B24" s="4">
+        <v>6</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="16">
+        <v>3.2290000000000001</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1.276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B25" s="4">
+        <v>6</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B26" s="4">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="16">
+        <v>1.629</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1.4019999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B27" s="4">
+        <v>7</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B28" s="4">
+        <v>7</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="16">
+        <v>3.306</v>
+      </c>
+      <c r="H28" s="17">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B29" s="4">
+        <v>7</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="16">
+        <v>0.105</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B30" s="4">
+        <v>8</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="16">
+        <v>1.526</v>
+      </c>
+      <c r="H30" s="17">
+        <v>1.1950000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B31" s="4">
+        <v>8</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H31" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B32" s="4">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="16">
+        <v>3.4470000000000001</v>
+      </c>
+      <c r="H32" s="17">
+        <v>1.4370000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B33" s="4">
+        <v>8</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="16">
+        <v>0.105</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B34" s="4">
+        <v>9</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="16">
+        <v>1.64</v>
+      </c>
+      <c r="H34" s="17">
+        <v>1.3049999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B35" s="4">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H35" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B36" s="4">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="16">
+        <v>3.6320000000000001</v>
+      </c>
+      <c r="H36" s="17">
+        <v>1.4490000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B37" s="4">
+        <v>9</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B38" s="4">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="16">
+        <v>1.8160000000000001</v>
+      </c>
+      <c r="H38" s="17">
+        <v>1.4730000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B39" s="4">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H39" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B40" s="4">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="16">
+        <v>3.7</v>
+      </c>
+      <c r="H40" s="17">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B41" s="4">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B42" s="4">
+        <v>11</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="16">
+        <v>1.9530000000000001</v>
+      </c>
+      <c r="H42" s="17">
+        <v>1.619</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B43" s="4">
+        <v>11</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B44" s="4">
+        <v>11</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="16">
+        <v>3.7440000000000002</v>
+      </c>
+      <c r="H44" s="17">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B45" s="4">
+        <v>11</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B46" s="4">
+        <v>12</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="5">
+        <v>8287</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="16">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="H46" s="17">
+        <v>1.768</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B47" s="4">
+        <v>12</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="5">
+        <v>10071</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H47" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="29" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B48" s="4">
+        <v>12</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="5">
+        <v>11843</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="16">
+        <v>3.8149999999999999</v>
+      </c>
+      <c r="H48" s="17">
+        <v>1.819</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="43" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B49" s="4">
+        <v>12</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="5">
+        <v>19547</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="16">
+        <v>0.159</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A112CC7-A14D-5E4F-9FEB-F774D4138DD7}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4772,7 +6067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FE680B-B3D8-9B43-A3A4-982C8339B97E}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
